--- a/datasets/production-like-corpus/corpus/engineering/OPS-003_服务等级与生产事故等级标准.xlsx
+++ b/datasets/production-like-corpus/corpus/engineering/OPS-003_服务等级与生产事故等级标准.xlsx
@@ -538,7 +538,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文档ID：OPS-003    版本：V3.2    归口部门：OPERATIONS    生效日：2026-01-20</t>
+          <t>文档编号：NT-OPER-MAT-2026-003    版本：V3.2    归口部门：OPERATIONS    生效日：2026-01-20</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文档ID：OPS-003    版本：V3.2    归口部门：OPERATIONS    生效日：2026-01-20</t>
+          <t>文档编号：NT-OPER-MAT-2026-003    版本：V3.2    归口部门：OPERATIONS    生效日：2026-01-20</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>OPS-005：P1首次响应≤10分钟</t>
+          <t>P1首次响应≤10分钟</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文档ID：OPS-003    版本：V3.2    归口部门：OPERATIONS    生效日：2026-01-20</t>
+          <t>文档编号：NT-OPER-MAT-2026-003    版本：V3.2    归口部门：OPERATIONS    生效日：2026-01-20</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -906,7 +906,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文档ID：OPS-003    版本：V3.2    归口部门：OPERATIONS    生效日：2026-01-20</t>
+          <t>文档编号：NT-OPER-MAT-2026-003    版本：V3.2    归口部门：OPERATIONS    生效日：2026-01-20</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>OPS-021：属于P0</t>
+          <t>核心支付整体不可用属于P0</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>OPS-020：不当然属于P0</t>
+          <t>数据库慢但未导致核心业务不可用不当然属于P0</t>
         </is>
       </c>
     </row>
